--- a/Luban/MiniTemplate/Datas/__tables__.xlsx
+++ b/Luban/MiniTemplate/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2E4B08-B84E-4C0A-93AB-1CD223CA61A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFFD4D4-E7FD-4D4C-916C-E84FFDF44B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="1305" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,14 +114,6 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>activity.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Activity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>TbItem</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -134,7 +126,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TbActivity</t>
+    <t>TbRoom</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Room</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>room.xlsx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -592,30 +592,30 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Luban/MiniTemplate/Datas/__tables__.xlsx
+++ b/Luban/MiniTemplate/Datas/__tables__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFFD4D4-E7FD-4D4C-916C-E84FFDF44B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C551CF-689A-46A7-B3A1-308D3B31FC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -135,6 +135,18 @@
   </si>
   <si>
     <t>room.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfigData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConfigData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBConfigData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -618,6 +630,20 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Luban/MiniTemplate/Datas/__tables__.xlsx
+++ b/Luban/MiniTemplate/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLTech\Documents\UnityProjects\SKnight\Luban\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C551CF-689A-46A7-B3A1-308D3B31FC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73774AB6-75EC-4209-90EC-6F5F23E6C3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5175" yWindow="1290" windowWidth="22980" windowHeight="12195" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>TBConfigData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TBLevel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>level.xlsx</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -502,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -644,6 +656,20 @@
         <v>34</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
